--- a/data/processed/sakila/metrics/combined_search_top_5_combined.xlsx
+++ b/data/processed/sakila/metrics/combined_search_top_5_combined.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,13 +457,45 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.2904015401540151</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.2674184085075174</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.4466446644664466</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2592278275446591</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2375870920425376</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4312431243124312</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>technical</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2474797876613056</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2278877887788778</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.385038503850385</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/sakila/metrics/combined_search_top_5_combined.xlsx
+++ b/data/processed/sakila/metrics/combined_search_top_5_combined.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2904015401540151</v>
+        <v>0.2674184085075174</v>
       </c>
       <c r="C2" t="n">
         <v>0.2674184085075174</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2592278275446591</v>
+        <v>0.2375870920425376</v>
       </c>
       <c r="C3" t="n">
         <v>0.2375870920425376</v>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2474797876613056</v>
+        <v>0.2278877887788778</v>
       </c>
       <c r="C4" t="n">
         <v>0.2278877887788778</v>
